--- a/syn/results/synthesis_results.xlsx
+++ b/syn/results/synthesis_results.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Summary_All" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="sobel_stochastic" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="prewitt_stochastic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="sobel_traditional" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="prewitt_stochastic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="prewitt_traditional" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,11 +441,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -1219,7 +1221,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1296,7 +1298,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1373,7 +1375,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1450,7 +1452,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1523,7 +1525,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1596,7 +1598,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1639,7 +1641,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1712,7 +1714,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>prewitt_stochastic</t>
+          <t>sobel_traditional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1780,75 +1782,1353 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>clk,clk_100mhz</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>135.317</v>
+      </c>
+      <c r="F19" t="n">
+        <v>90.1481</v>
+      </c>
+      <c r="G19" t="n">
+        <v>45.1688</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.6726</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1206</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1052</v>
+      </c>
+      <c r="K19" t="n">
+        <v>154</v>
+      </c>
+      <c r="L19" t="n">
+        <v>208.3726</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="N19" t="n">
+        <v>208.4814</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>953.3147</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="S19" t="n">
+        <v>22</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>address_mux</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="I20" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.0698</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.0718</v>
+      </c>
+      <c r="O20" t="n">
+        <v>697.8784000000001</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>202.1216</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.3099</v>
+      </c>
+      <c r="S20" t="n">
+        <v>39</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>data_MUX</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="O21" t="n">
+        <v>771.1016</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>128.8985</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.3688</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>camera_reset_clk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="O22" t="n">
+        <v>794.2994</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>105.7005</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.8614</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>capture_starter</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>vsync</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.2037</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="O23" t="n">
+        <v>786.9304</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>63.0696</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4.6933</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>clk_100mhz,pclk</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>30.4285</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11.941</v>
+      </c>
+      <c r="G24" t="n">
+        <v>18.4874</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.6244</v>
+      </c>
+      <c r="I24" t="n">
+        <v>224</v>
+      </c>
+      <c r="J24" t="n">
+        <v>175</v>
+      </c>
+      <c r="K24" t="n">
+        <v>49</v>
+      </c>
+      <c r="L24" t="n">
+        <v>26.1672</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N24" t="n">
+        <v>26.1878</v>
+      </c>
+      <c r="O24" t="n">
+        <v>768.5003</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>81.4997</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4.3197</v>
+      </c>
+      <c r="S24" t="n">
+        <v>14</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>frame_buffer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>read_write_controller</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3.4992</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.6038</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.8954</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" t="n">
+        <v>25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.5633</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7.5658</v>
+      </c>
+      <c r="O26" t="n">
+        <v>731.6534</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>118.3466</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.7265</v>
+      </c>
+      <c r="S26" t="n">
+        <v>11</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>vga_display</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prewitt_stochastic</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>clk_100mhz,p_clk</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>17.9917</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.8269</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.1648</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.5017</v>
+      </c>
+      <c r="I27" t="n">
+        <v>147</v>
+      </c>
+      <c r="J27" t="n">
+        <v>125</v>
+      </c>
+      <c r="K27" t="n">
+        <v>22</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29.8111</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N27" t="n">
+        <v>29.8246</v>
+      </c>
+      <c r="O27" t="n">
+        <v>343.205</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>506.795</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>sobel_stoch</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>prewitt_stochastic</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>clk,clk_100mhz</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>106.4048</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F28" t="n">
         <v>70.5672</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G28" t="n">
         <v>35.8376</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H28" t="n">
         <v>9.025</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I28" t="n">
         <v>980</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J28" t="n">
         <v>858</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K28" t="n">
         <v>122</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L28" t="n">
         <v>165.7759</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M28" t="n">
         <v>0.0842</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N28" t="n">
         <v>165.8601</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O28" t="n">
         <v>0.4294</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
         <v>955.9796</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R28" t="n">
         <v>1.0004</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S28" t="n">
         <v>27</v>
       </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>address_mux</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="I29" t="n">
+        <v>19</v>
+      </c>
+      <c r="J29" t="n">
+        <v>19</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.0698</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.0718</v>
+      </c>
+      <c r="O29" t="n">
+        <v>697.8784000000001</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>202.1216</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.3099</v>
+      </c>
+      <c r="S29" t="n">
+        <v>39</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>data_MUX</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="O30" t="n">
+        <v>771.1016</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>128.8985</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4.3688</v>
+      </c>
+      <c r="S30" t="n">
+        <v>13</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>camera_reset_clk</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="O31" t="n">
+        <v>794.2994</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>105.7005</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4.8614</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>capture_starter</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>vsync</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.2037</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="O32" t="n">
+        <v>786.9304</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>63.0696</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4.6933</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>clk_100mhz,pclk</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>30.4285</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11.941</v>
+      </c>
+      <c r="G33" t="n">
+        <v>18.4874</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.6244</v>
+      </c>
+      <c r="I33" t="n">
+        <v>224</v>
+      </c>
+      <c r="J33" t="n">
+        <v>175</v>
+      </c>
+      <c r="K33" t="n">
+        <v>49</v>
+      </c>
+      <c r="L33" t="n">
+        <v>26.1672</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N33" t="n">
+        <v>26.1878</v>
+      </c>
+      <c r="O33" t="n">
+        <v>768.5003</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>81.4997</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4.3197</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>frame_buffer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>read_write_controller</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3.4992</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.6038</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.8954</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="I35" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" t="n">
+        <v>25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.5633</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7.5658</v>
+      </c>
+      <c r="O35" t="n">
+        <v>731.6534</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>118.3466</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.7265</v>
+      </c>
+      <c r="S35" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>vga_display</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>clk_100mhz,p_clk</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>17.9917</v>
+      </c>
+      <c r="F36" t="n">
+        <v>9.8269</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.1648</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.5017</v>
+      </c>
+      <c r="I36" t="n">
+        <v>147</v>
+      </c>
+      <c r="J36" t="n">
+        <v>125</v>
+      </c>
+      <c r="K36" t="n">
+        <v>22</v>
+      </c>
+      <c r="L36" t="n">
+        <v>29.8111</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N36" t="n">
+        <v>29.8246</v>
+      </c>
+      <c r="O36" t="n">
+        <v>343.205</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>506.795</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>prewitt</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>clk,clk_100mhz</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>139.7201</v>
+      </c>
+      <c r="F37" t="n">
+        <v>94.5513</v>
+      </c>
+      <c r="G37" t="n">
+        <v>45.1688</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11.6786</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1248</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1094</v>
+      </c>
+      <c r="K37" t="n">
+        <v>154</v>
+      </c>
+      <c r="L37" t="n">
+        <v>209.0839</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="N37" t="n">
+        <v>209.1961</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.5522</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>952.9457</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="S37" t="n">
+        <v>22</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2648,6 +3928,789 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source file (module)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Clocks</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total cell area (um2)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Comb area (um2)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Noncomb area (um2)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Buf/Inv area (um2)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t># cells</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t># comb cells</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t># seq cells</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Dyn power (uW)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Leak power (uW)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Total power (uW)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Worst slack (ps)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Slack met</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Crit path (ps)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Est Fmax (GHz)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t># warnings</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t># errors</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>address_mux</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.0698</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.0718</v>
+      </c>
+      <c r="O2" t="n">
+        <v>697.8784000000001</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>202.1216</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.3099</v>
+      </c>
+      <c r="S2" t="n">
+        <v>39</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>data_MUX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="O3" t="n">
+        <v>771.1016</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>128.8985</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.3688</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>camera_reset_clk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="O4" t="n">
+        <v>794.2994</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>105.7005</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.8614</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>capture_starter</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>vsync</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.2037</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="O5" t="n">
+        <v>786.9304</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>63.0696</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.6933</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>clk_100mhz,pclk</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>30.4285</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.941</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18.4874</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.6244</v>
+      </c>
+      <c r="I6" t="n">
+        <v>224</v>
+      </c>
+      <c r="J6" t="n">
+        <v>175</v>
+      </c>
+      <c r="K6" t="n">
+        <v>49</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26.1672</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26.1878</v>
+      </c>
+      <c r="O6" t="n">
+        <v>768.5003</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>81.4997</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.3197</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frame_buffer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>read_write_controller</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3.4992</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.6038</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.8954</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.5633</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.5658</v>
+      </c>
+      <c r="O8" t="n">
+        <v>731.6534</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>118.3466</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.7265</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vga_display</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>clk_100mhz,p_clk</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17.9917</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.8269</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.1648</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5017</v>
+      </c>
+      <c r="I9" t="n">
+        <v>147</v>
+      </c>
+      <c r="J9" t="n">
+        <v>125</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22</v>
+      </c>
+      <c r="L9" t="n">
+        <v>29.8111</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N9" t="n">
+        <v>29.8246</v>
+      </c>
+      <c r="O9" t="n">
+        <v>343.205</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>506.795</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sobel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sobel_traditional</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>clk,clk_100mhz</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>135.317</v>
+      </c>
+      <c r="F10" t="n">
+        <v>90.1481</v>
+      </c>
+      <c r="G10" t="n">
+        <v>45.1688</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.6726</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1206</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1052</v>
+      </c>
+      <c r="K10" t="n">
+        <v>154</v>
+      </c>
+      <c r="L10" t="n">
+        <v>208.3726</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="N10" t="n">
+        <v>208.4814</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>953.3147</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -3419,4 +5482,787 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source file (module)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Clocks</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total cell area (um2)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Comb area (um2)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Noncomb area (um2)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Buf/Inv area (um2)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t># cells</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t># comb cells</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t># seq cells</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Dyn power (uW)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Leak power (uW)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Total power (uW)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Worst slack (ps)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Slack met</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Crit path (ps)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Est Fmax (GHz)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t># warnings</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t># errors</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>address_mux</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.3328</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.0698</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.0718</v>
+      </c>
+      <c r="O2" t="n">
+        <v>697.8784000000001</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>202.1216</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.3099</v>
+      </c>
+      <c r="S2" t="n">
+        <v>39</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>data_MUX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="O3" t="n">
+        <v>771.1016</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>128.8985</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.3688</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>camera_reset_clk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>comb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="O4" t="n">
+        <v>794.2994</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>105.7005</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.8614</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>combinational (no registers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>capture_starter</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>vsync</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.2037</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="O5" t="n">
+        <v>786.9304</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>63.0696</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.6933</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>clk_100mhz,pclk</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>30.4285</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.941</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18.4874</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.6244</v>
+      </c>
+      <c r="I6" t="n">
+        <v>224</v>
+      </c>
+      <c r="J6" t="n">
+        <v>175</v>
+      </c>
+      <c r="K6" t="n">
+        <v>49</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26.1672</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26.1878</v>
+      </c>
+      <c r="O6" t="n">
+        <v>768.5003</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>81.4997</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.3197</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frame_buffer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>read_write_controller</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>clk</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3.4992</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.6038</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.8954</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.5633</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.5658</v>
+      </c>
+      <c r="O8" t="n">
+        <v>731.6534</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>118.3466</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.7265</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vga_display</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>clk_100mhz,p_clk</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17.9917</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.8269</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.1648</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5017</v>
+      </c>
+      <c r="I9" t="n">
+        <v>147</v>
+      </c>
+      <c r="J9" t="n">
+        <v>125</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22</v>
+      </c>
+      <c r="L9" t="n">
+        <v>29.8111</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N9" t="n">
+        <v>29.8246</v>
+      </c>
+      <c r="O9" t="n">
+        <v>343.205</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>506.795</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>prewitt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prewitt_traditional</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>clk,clk_100mhz</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>139.7201</v>
+      </c>
+      <c r="F10" t="n">
+        <v>94.5513</v>
+      </c>
+      <c r="G10" t="n">
+        <v>45.1688</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.6786</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1248</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1094</v>
+      </c>
+      <c r="K10" t="n">
+        <v>154</v>
+      </c>
+      <c r="L10" t="n">
+        <v>209.0839</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="N10" t="n">
+        <v>209.1961</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5522</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>952.9457</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>